--- a/Orçado/Orça-Seringal/ESPLANADA SERINGAL.xlsx
+++ b/Orçado/Orça-Seringal/ESPLANADA SERINGAL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\henrique.santos\orcamento2027\budgetflow-insights\Orçado\Orça-Seringal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BFCF4980-C1FE-4CF3-8A9E-19AA8FDBBC15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F983A65-97CF-41BB-8EFF-47BEC11DBAEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20520" yWindow="1920" windowWidth="20640" windowHeight="11040" xr2:uid="{8331C052-5CFE-4952-B369-06C2E6549A49}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8331C052-5CFE-4952-B369-06C2E6549A49}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="98">
   <si>
     <t>4.1.01.01.0001</t>
   </si>
@@ -59,9 +59,6 @@
     <t>4.1.01.02.0030</t>
   </si>
   <si>
-    <t>4.1.01.03.0004</t>
-  </si>
-  <si>
     <t>4.1.01.04.0001</t>
   </si>
   <si>
@@ -146,9 +143,6 @@
     <t>4.1.01.03-LOCACOES</t>
   </si>
   <si>
-    <t>LOCAÇÕES DE MÁQUINAS AGRÍCOLAS</t>
-  </si>
-  <si>
     <t>4.1.01.04-MANUTENCAO E CONSERVACAO DE BENS</t>
   </si>
   <si>
@@ -237,6 +231,108 @@
   </si>
   <si>
     <t>Descrição C. Contábil</t>
+  </si>
+  <si>
+    <t>RATEIO CARRETAS AGRICOLAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RATEIO CARRETAS AGRICOLAS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RATEIO CARRETAS TANQUE </t>
+  </si>
+  <si>
+    <t>RATEIO CONFRATERNIZACOES E EVENTOS COM COLABORADORES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RATEIO MEDICINA E SEGURANCA DO TRABALHO </t>
+  </si>
+  <si>
+    <t>RATEIO MOTOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RATEIO OFICINA </t>
+  </si>
+  <si>
+    <t>RATEIO PROGRAMA INTEGRIDADE</t>
+  </si>
+  <si>
+    <t>RATEIO PROJETOS DESENVOLVIMENTO HUMANO</t>
+  </si>
+  <si>
+    <t>RATEIO PULVERIZADORES</t>
+  </si>
+  <si>
+    <t>RATEIO RECEBIDO</t>
+  </si>
+  <si>
+    <t>RATEIO SUPERVISAO SERINGUEIRA</t>
+  </si>
+  <si>
+    <t>RATEIO TRATORES LEVES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RATEIO TRATORES MEDIOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RATEIO VEICULOS LEVES </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RATEIO VEICULOS MEDIOS </t>
+  </si>
+  <si>
+    <t>4.2.01.02.0034</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0045</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0017</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0018</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0024</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0052</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0064</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0047</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0035</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0020</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0066</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0051</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0036</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0037</t>
+  </si>
+  <si>
+    <t>4.2.01.02.0021</t>
+  </si>
+  <si>
+    <t>LOCACOES DE MAQUINAS AGRICOLAS</t>
+  </si>
+  <si>
+    <t>4.1.01.03.0002 </t>
+  </si>
+  <si>
+    <t>FRETES E CARRETOS PJ</t>
   </si>
 </sst>
 </file>
@@ -676,12 +772,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{963C40D5-EB36-435F-AA3B-B322C55C16E7}">
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="48.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="8" width="10.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="10" max="15" width="10.109375" style="5" bestFit="1" customWidth="1"/>
@@ -690,13 +786,13 @@
   <sheetData>
     <row r="1" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>65</v>
       </c>
       <c r="D1" s="4">
         <v>46113</v>
@@ -737,13 +833,13 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D2" s="5">
         <v>153252.81098190183</v>
@@ -784,13 +880,13 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" s="5">
         <v>802.51</v>
@@ -831,13 +927,13 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" s="5">
         <v>7315.1221291630045</v>
@@ -878,13 +974,13 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>97</v>
       </c>
       <c r="D5" s="5">
         <v>756.01499999999999</v>
@@ -925,13 +1021,13 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D6" s="5">
         <v>0</v>
@@ -954,13 +1050,13 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H7" s="5">
         <v>160.50200000000001</v>
@@ -977,13 +1073,13 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>6</v>
+        <v>96</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="D8" s="5">
         <v>6785.6134499999998</v>
@@ -1024,13 +1120,13 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D9" s="5">
         <v>910.88</v>
@@ -1071,13 +1167,13 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
         <v>36</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" t="s">
-        <v>38</v>
       </c>
       <c r="D10" s="5">
         <v>606.46</v>
@@ -1118,13 +1214,13 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D11" s="5">
         <v>750.49</v>
@@ -1165,13 +1261,13 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D12" s="5">
         <v>65.45</v>
@@ -1212,13 +1308,13 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D13" s="5">
         <v>1425.3485599999999</v>
@@ -1259,13 +1355,13 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D14" s="5">
         <v>564.9</v>
@@ -1306,13 +1402,13 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D15" s="5">
         <v>18446.45</v>
@@ -1353,13 +1449,13 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K16" s="5">
         <v>0</v>
@@ -1373,13 +1469,13 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" t="s">
         <v>45</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" t="s">
-        <v>47</v>
       </c>
       <c r="N17" s="5">
         <v>0</v>
@@ -1387,13 +1483,13 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H18" s="5">
         <v>0</v>
@@ -1404,13 +1500,13 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D19" s="5">
         <v>820.93</v>
@@ -1451,13 +1547,13 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="J20" s="5">
         <v>0</v>
@@ -1465,13 +1561,13 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" t="s">
         <v>51</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" t="s">
-        <v>53</v>
       </c>
       <c r="D21" s="5">
         <v>21</v>
@@ -1512,13 +1608,13 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C22" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D22" s="5">
         <v>3364.1</v>
@@ -1559,13 +1655,13 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C23" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D23" s="5">
         <v>1428.85</v>
@@ -1606,13 +1702,13 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" t="s">
         <v>55</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24" t="s">
-        <v>57</v>
       </c>
       <c r="D24" s="5">
         <v>30.66</v>
@@ -1653,13 +1749,13 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C25" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D25" s="5">
         <v>8284.1678499999998</v>
@@ -1700,13 +1796,13 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C26" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D26" s="5">
         <v>218.68</v>
@@ -1747,13 +1843,13 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C27" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D27" s="5">
         <v>419.1</v>
@@ -1794,49 +1890,435 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="C28" t="s">
-        <v>62</v>
-      </c>
-      <c r="D28" s="5">
-        <v>36020.336015643334</v>
-      </c>
-      <c r="E28" s="5">
-        <v>36626.161973437738</v>
-      </c>
-      <c r="F28" s="5">
-        <v>37766.435426624899</v>
+        <v>64</v>
       </c>
       <c r="G28" s="5">
-        <v>40142.215720184897</v>
+        <v>284.51169999999996</v>
       </c>
       <c r="H28" s="5">
-        <v>37099.396713584894</v>
-      </c>
-      <c r="I28" s="5">
+        <v>284.51169999999996</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>59</v>
+      </c>
+      <c r="B29" t="s">
+        <v>80</v>
+      </c>
+      <c r="C29" t="s">
+        <v>65</v>
+      </c>
+      <c r="D29" s="5">
+        <v>272.26</v>
+      </c>
+      <c r="E29" s="5">
+        <v>284.51169999999996</v>
+      </c>
+      <c r="F29" s="5">
+        <v>284.51169999999996</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" t="s">
+        <v>81</v>
+      </c>
+      <c r="C30" t="s">
+        <v>66</v>
+      </c>
+      <c r="D30" s="5">
+        <v>0</v>
+      </c>
+      <c r="E30" s="5">
+        <v>124.35499999999999</v>
+      </c>
+      <c r="F30" s="5">
+        <v>124.35499999999999</v>
+      </c>
+      <c r="G30" s="5">
+        <v>124.35499999999999</v>
+      </c>
+      <c r="H30" s="5">
+        <v>124.35499999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>59</v>
+      </c>
+      <c r="B31" t="s">
+        <v>82</v>
+      </c>
+      <c r="C31" t="s">
+        <v>67</v>
+      </c>
+      <c r="D31" s="5">
+        <v>163.20000000000002</v>
+      </c>
+      <c r="E31" s="5">
+        <v>172.20000000000002</v>
+      </c>
+      <c r="F31" s="5">
+        <v>883.80000000000007</v>
+      </c>
+      <c r="G31" s="5">
+        <v>121.79999999999998</v>
+      </c>
+      <c r="H31" s="5">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>59</v>
+      </c>
+      <c r="B32" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" s="5">
+        <v>1288.32</v>
+      </c>
+      <c r="E32" s="5">
+        <v>1288.32</v>
+      </c>
+      <c r="F32" s="5">
+        <v>1288.32</v>
+      </c>
+      <c r="G32" s="5">
+        <v>1288.32</v>
+      </c>
+      <c r="H32" s="5">
+        <v>1288.32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>59</v>
+      </c>
+      <c r="B33" t="s">
+        <v>89</v>
+      </c>
+      <c r="C33" t="s">
+        <v>69</v>
+      </c>
+      <c r="D33" s="5">
+        <v>368.88</v>
+      </c>
+      <c r="E33" s="5">
+        <v>385.47959999999995</v>
+      </c>
+      <c r="F33" s="5">
+        <v>385.47959999999995</v>
+      </c>
+      <c r="G33" s="5">
+        <v>385.47959999999995</v>
+      </c>
+      <c r="H33" s="5">
+        <v>385.47959999999995</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>59</v>
+      </c>
+      <c r="B34" t="s">
+        <v>84</v>
+      </c>
+      <c r="C34" t="s">
+        <v>70</v>
+      </c>
+      <c r="D34" s="5">
+        <v>471.15</v>
+      </c>
+      <c r="E34" s="5">
+        <v>492.35174999999992</v>
+      </c>
+      <c r="F34" s="5">
+        <v>492.35174999999992</v>
+      </c>
+      <c r="G34" s="5">
+        <v>492.35174999999992</v>
+      </c>
+      <c r="H34" s="5">
+        <v>492.35174999999992</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>59</v>
+      </c>
+      <c r="B35" t="s">
+        <v>85</v>
+      </c>
+      <c r="C35" t="s">
+        <v>60</v>
+      </c>
+      <c r="D35" s="5">
+        <v>624.23</v>
+      </c>
+      <c r="E35" s="5">
+        <v>624.23</v>
+      </c>
+      <c r="F35" s="5">
+        <v>624.23</v>
+      </c>
+      <c r="G35" s="5">
+        <v>624.23</v>
+      </c>
+      <c r="H35" s="5">
+        <v>624.23</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>59</v>
+      </c>
+      <c r="B36" t="s">
+        <v>86</v>
+      </c>
+      <c r="C36" t="s">
+        <v>71</v>
+      </c>
+      <c r="D36" s="5">
+        <v>229.54</v>
+      </c>
+      <c r="E36" s="5">
+        <v>239.86929999999998</v>
+      </c>
+      <c r="F36" s="5">
+        <v>239.86929999999998</v>
+      </c>
+      <c r="G36" s="5">
+        <v>239.86929999999998</v>
+      </c>
+      <c r="H36" s="5">
+        <v>239.86929999999998</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>59</v>
+      </c>
+      <c r="B37" t="s">
+        <v>90</v>
+      </c>
+      <c r="C37" t="s">
+        <v>72</v>
+      </c>
+      <c r="D37" s="5">
+        <v>257.35000000000002</v>
+      </c>
+      <c r="E37" s="5">
+        <v>268.93074999999999</v>
+      </c>
+      <c r="F37" s="5">
+        <v>268.93074999999999</v>
+      </c>
+      <c r="G37" s="5">
+        <v>268.93074999999999</v>
+      </c>
+      <c r="H37" s="5">
+        <v>268.93074999999999</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>59</v>
+      </c>
+      <c r="B38" t="s">
+        <v>87</v>
+      </c>
+      <c r="C38" t="s">
+        <v>73</v>
+      </c>
+      <c r="D38" s="5">
+        <v>242.67</v>
+      </c>
+      <c r="E38" s="5">
+        <v>253.59014999999997</v>
+      </c>
+      <c r="F38" s="5">
+        <v>253.59014999999997</v>
+      </c>
+      <c r="G38" s="5">
+        <v>253.59014999999997</v>
+      </c>
+      <c r="H38" s="5">
+        <v>253.59014999999997</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>59</v>
+      </c>
+      <c r="B39" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" t="s">
+        <v>74</v>
+      </c>
+      <c r="I39" s="5">
         <v>38487.230642581773</v>
       </c>
-      <c r="J28" s="5">
+      <c r="J39" s="5">
         <v>39238.270642581774</v>
       </c>
-      <c r="K28" s="5">
+      <c r="K39" s="5">
         <v>56700.503682457776</v>
       </c>
-      <c r="L28" s="5">
+      <c r="L39" s="5">
         <v>47084.352370221779</v>
       </c>
-      <c r="M28" s="5">
+      <c r="M39" s="5">
         <v>38465.871724716024</v>
       </c>
-      <c r="N28" s="5">
+      <c r="N39" s="5">
         <v>38091.961181904706</v>
       </c>
-      <c r="O28" s="5">
+      <c r="O39" s="5">
         <v>39891.345931736709</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>59</v>
+      </c>
+      <c r="B40" t="s">
+        <v>91</v>
+      </c>
+      <c r="C40" t="s">
+        <v>75</v>
+      </c>
+      <c r="D40" s="5">
+        <v>6445.4060156433334</v>
+      </c>
+      <c r="E40" s="5">
+        <v>6737.9138734377339</v>
+      </c>
+      <c r="F40" s="5">
+        <v>7166.5873266248973</v>
+      </c>
+      <c r="G40" s="5">
+        <v>10304.367620184898</v>
+      </c>
+      <c r="H40" s="5">
+        <v>7342.848613584898</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>59</v>
+      </c>
+      <c r="B41" t="s">
+        <v>88</v>
+      </c>
+      <c r="C41" t="s">
+        <v>76</v>
+      </c>
+      <c r="D41" s="5">
+        <v>0</v>
+      </c>
+      <c r="E41" s="5">
+        <v>0</v>
+      </c>
+      <c r="F41" s="5">
+        <v>0</v>
+      </c>
+      <c r="G41" s="5">
+        <v>0</v>
+      </c>
+      <c r="H41" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>59</v>
+      </c>
+      <c r="B42" t="s">
+        <v>92</v>
+      </c>
+      <c r="C42" t="s">
+        <v>77</v>
+      </c>
+      <c r="D42" s="5">
+        <v>3500</v>
+      </c>
+      <c r="E42" s="5">
+        <v>3500</v>
+      </c>
+      <c r="F42" s="5">
+        <v>3500</v>
+      </c>
+      <c r="G42" s="5">
+        <v>3500</v>
+      </c>
+      <c r="H42" s="5">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>59</v>
+      </c>
+      <c r="B43" t="s">
+        <v>93</v>
+      </c>
+      <c r="C43" t="s">
+        <v>78</v>
+      </c>
+      <c r="D43" s="5">
+        <v>2157.33</v>
+      </c>
+      <c r="E43" s="5">
+        <v>2254.4098499999996</v>
+      </c>
+      <c r="F43" s="5">
+        <v>2254.4098499999996</v>
+      </c>
+      <c r="G43" s="5">
+        <v>2254.4098499999996</v>
+      </c>
+      <c r="H43" s="5">
+        <v>2254.4098499999996</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>59</v>
+      </c>
+      <c r="B44" t="s">
+        <v>94</v>
+      </c>
+      <c r="C44" t="s">
+        <v>79</v>
+      </c>
+      <c r="D44" s="5">
+        <v>20000</v>
+      </c>
+      <c r="E44" s="5">
+        <v>20000</v>
+      </c>
+      <c r="F44" s="5">
+        <v>20000</v>
+      </c>
+      <c r="G44" s="5">
+        <v>20000</v>
+      </c>
+      <c r="H44" s="5">
+        <v>20000</v>
       </c>
     </row>
   </sheetData>
